--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="89">
   <si>
     <t>Sezione</t>
   </si>
@@ -140,10 +140,16 @@
     <t>Ente dichiarante</t>
   </si>
   <si>
+    <t>Data formazione documento</t>
+  </si>
+  <si>
+    <t>evento.enteDichiarante</t>
+  </si>
+  <si>
+    <t>dataTrascrizione</t>
+  </si>
+  <si>
     <t>Estremi documento</t>
-  </si>
-  <si>
-    <t>evento.enteDichiarante</t>
   </si>
   <si>
     <t>estremiDocumento</t>
@@ -331,7 +337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -696,7 +702,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>43</v>
@@ -719,7 +725,7 @@
         <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>43</v>
@@ -742,7 +748,7 @@
         <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>43</v>
@@ -788,7 +794,7 @@
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>43</v>
@@ -943,19 +949,19 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -966,16 +972,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>70</v>
@@ -989,7 +995,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -998,7 +1004,7 @@
         <v>13</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>72</v>
@@ -1012,7 +1018,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>73</v>
@@ -1021,7 +1027,7 @@
         <v>13</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>74</v>
@@ -1035,7 +1041,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>75</v>
@@ -1044,7 +1050,7 @@
         <v>13</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>76</v>
@@ -1058,7 +1064,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>77</v>
@@ -1067,10 +1073,10 @@
         <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1081,19 +1087,19 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
@@ -1104,7 +1110,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>80</v>
@@ -1113,10 +1119,10 @@
         <v>13</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>10</v>
@@ -1127,19 +1133,19 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
@@ -1150,7 +1156,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>83</v>
@@ -1159,7 +1165,7 @@
         <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>84</v>
@@ -1173,13 +1179,13 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>17</v>
@@ -1191,6 +1197,29 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>19</v>
       </c>
     </row>
